--- a/Jupyter_Notebooks_and_Other_Files/03_Deep_Dives/03_02_Applications/03_02_05_WRF_and_MPAS_Domain_Mapping/time_series_station_files_3_dom_all.xlsx
+++ b/Jupyter_Notebooks_and_Other_Files/03_Deep_Dives/03_02_Applications/03_02_05_WRF_and_MPAS_Domain_Mapping/time_series_station_files_3_dom_all.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wjc/GitHub/AES_CEE_Python/Jupyter_Notebooks_and_Other_Files/03_Deep_Dives/03_02_Applications/03_02_05_WRF_and_MPAS_Domain_Mapping/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wjc/GitHub/SD_Mines_WRF_REALTIME/namelist_files_and_local_scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A3D2A4-A28F-FE42-9449-28451F8B33EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C626BFCA-A5CA-9645-986B-FFB29F8BBF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="880" yWindow="2220" windowWidth="26000" windowHeight="16820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7440" yWindow="1740" windowWidth="26000" windowHeight="16820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
   <si>
     <t>Station ID</t>
   </si>
@@ -398,9 +398,6 @@
     <t>HTML Code</t>
   </si>
   <si>
-    <t>KBHK </t>
-  </si>
-  <si>
     <t>Baker Airport, MT</t>
   </si>
   <si>
@@ -408,6 +405,15 @@
   </si>
   <si>
     <t>Ekalaka Airport, WY</t>
+  </si>
+  <si>
+    <t>KHON</t>
+  </si>
+  <si>
+    <t>Huron Airport, SD</t>
+  </si>
+  <si>
+    <t>KBHK</t>
   </si>
 </sst>
 </file>
@@ -784,7 +790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19"/>
   <cols>
     <col min="1" max="2" width="29.5" style="3" customWidth="1"/>
@@ -820,9 +826,8 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="3" t="e">
-        <f>1+A1</f>
-        <v>#VALUE!</v>
+      <c r="A2" s="3">
+        <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>6</v>
@@ -848,9 +853,9 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="3" t="e">
+      <c r="A3" s="3">
         <f>1+A2</f>
-        <v>#VALUE!</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>7</v>
@@ -871,14 +876,14 @@
         <v>10.6829144055438</v>
       </c>
       <c r="H3" s="4" t="str">
-        <f t="shared" ref="H3:H59" si="0">CONCATENATE("        &lt;option value=""",B3,"""&gt;",B3,": ",D3,"&lt;/option&gt;")</f>
+        <f t="shared" ref="H3:H60" si="0">CONCATENATE("        &lt;option value=""",B3,"""&gt;",B3,": ",D3,"&lt;/option&gt;")</f>
         <v xml:space="preserve">        &lt;option value="KRCA"&gt;KRCA: Ellsworth AFB, SD&lt;/option&gt;</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="3" t="e">
-        <f>1+A3</f>
-        <v>#VALUE!</v>
+      <c r="A4" s="3">
+        <f t="shared" ref="A4:A60" si="1">1+A3</f>
+        <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>8</v>
@@ -904,9 +909,9 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="3" t="e">
-        <f>1+A4</f>
-        <v>#VALUE!</v>
+      <c r="A5" s="3">
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>9</v>
@@ -933,7 +938,8 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="3">
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>10</v>
@@ -960,8 +966,8 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="3">
-        <f>1+A6</f>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>11</v>
@@ -988,8 +994,8 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="3">
-        <f>1+A7</f>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>116</v>
@@ -1016,8 +1022,8 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="3">
-        <f>1+A8</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>12</v>
@@ -1044,8 +1050,8 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="3">
-        <f>1+A9</f>
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>114</v>
@@ -1072,8 +1078,8 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="3">
-        <f>1+A10</f>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>13</v>
@@ -1100,7 +1106,8 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="3">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>117</v>
@@ -1127,8 +1134,8 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="3">
-        <f>1+A12</f>
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>14</v>
@@ -1155,8 +1162,8 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="3">
-        <f>1+A13</f>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>15</v>
@@ -1183,8 +1190,8 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="3">
-        <f>1+A14</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>16</v>
@@ -1211,8 +1218,8 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="3">
-        <f>1+A15</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>17</v>
@@ -1239,7 +1246,8 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="3">
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>18</v>
@@ -1266,8 +1274,8 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="3">
-        <f>1+A17</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>19</v>
@@ -1294,7 +1302,8 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="3">
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>20</v>
@@ -1321,8 +1330,8 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="3">
-        <f>1+A19</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>21</v>
@@ -1349,7 +1358,8 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="3">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>22</v>
@@ -1376,7 +1386,8 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="3">
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>23</v>
@@ -1403,8 +1414,8 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="3">
-        <f>1+A22</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
@@ -1431,16 +1442,17 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="3">
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C24" s="3">
+        <v>2</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="C24" s="3">
-        <v>2</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="E24" s="3">
         <v>45.876485299999999</v>
@@ -1458,8 +1470,8 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="3">
-        <f>1+A24</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>25</v>
@@ -1486,8 +1498,8 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="3">
-        <f>1+A25</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>26</v>
@@ -1514,8 +1526,8 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="3">
-        <f>1+A26</f>
-        <v>11</v>
+        <f t="shared" si="1"/>
+        <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>27</v>
@@ -1542,8 +1554,8 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="3">
-        <f>1+A27</f>
-        <v>12</v>
+        <f t="shared" si="1"/>
+        <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>28</v>
@@ -1570,7 +1582,8 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="3">
-        <v>11</v>
+        <f t="shared" si="1"/>
+        <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>29</v>
@@ -1597,7 +1610,8 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="3">
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>30</v>
@@ -1624,8 +1638,8 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="3">
-        <f>1+A30</f>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>31</v>
@@ -1652,8 +1666,8 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="3">
-        <f>1+A31</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>32</v>
@@ -1680,8 +1694,8 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="3">
-        <f>1+A32</f>
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>33</v>
@@ -1708,8 +1722,8 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="3">
-        <f>1+A33</f>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>34</v>
@@ -1736,8 +1750,8 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="3">
-        <f>1+A34</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>35</v>
@@ -1764,7 +1778,8 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="3">
-        <v>12</v>
+        <f t="shared" si="1"/>
+        <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>36</v>
@@ -1791,8 +1806,8 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="3">
-        <f>1+A36</f>
-        <v>13</v>
+        <f t="shared" si="1"/>
+        <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>37</v>
@@ -1819,16 +1834,17 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="3">
-        <v>13</v>
+        <f t="shared" si="1"/>
+        <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C38" s="5">
+        <v>2</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>120</v>
-      </c>
-      <c r="C38" s="5">
-        <v>2</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>121</v>
       </c>
       <c r="E38" s="5">
         <v>46.346600000000002</v>
@@ -1841,13 +1857,13 @@
       </c>
       <c r="H38" s="4" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">        &lt;option value="KBHK "&gt;KBHK : Baker Airport, MT&lt;/option&gt;</v>
+        <v xml:space="preserve">        &lt;option value="KBHK"&gt;KBHK: Baker Airport, MT&lt;/option&gt;</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="3">
-        <f>1+A38</f>
-        <v>14</v>
+        <f t="shared" si="1"/>
+        <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>38</v>
@@ -1874,7 +1890,8 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="3">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>39</v>
@@ -1901,8 +1918,8 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="3">
-        <f>1+A40</f>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>40</v>
@@ -1929,8 +1946,8 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="3">
-        <f>1+A41</f>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>43</v>
@@ -1957,7 +1974,8 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="3">
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>41</v>
@@ -1984,8 +2002,8 @@
     </row>
     <row r="44" spans="1:8" s="3" customFormat="1">
       <c r="A44" s="3">
-        <f>1+A43</f>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>42</v>
@@ -2012,8 +2030,8 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="3">
-        <f>1+A44</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>44</v>
@@ -2040,391 +2058,420 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="3">
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="C46" s="3">
         <v>1</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="E46" s="3">
-        <v>45.4467</v>
+        <v>44.385199999999998</v>
       </c>
       <c r="F46" s="3">
-        <v>-98.422399999999996</v>
+        <v>-98.2286</v>
       </c>
       <c r="G46" s="3">
-        <v>407.2835821076373</v>
+        <v>387.7</v>
       </c>
       <c r="H46" s="4" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">        &lt;option value="KABR"&gt;KABR: Aberdeen NWS, SD&lt;/option&gt;</v>
+        <v xml:space="preserve">        &lt;option value="KHON"&gt;KHON: Huron Airport, SD&lt;/option&gt;</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="3">
-        <f>1+A46</f>
-        <v>11</v>
+        <f t="shared" si="1"/>
+        <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C47" s="3">
         <v>1</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E47" s="3">
-        <v>43.0642</v>
+        <v>45.4467</v>
       </c>
       <c r="F47" s="3">
-        <v>-108.46</v>
+        <v>-98.422399999999996</v>
       </c>
       <c r="G47" s="3">
-        <v>437.82235791428252</v>
+        <v>407.2835821076373</v>
       </c>
       <c r="H47" s="4" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">        &lt;option value="KRIW"&gt;KRIW: Riverton NWS, WY&lt;/option&gt;</v>
+        <v xml:space="preserve">        &lt;option value="KABR"&gt;KABR: Aberdeen NWS, SD&lt;/option&gt;</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="3">
-        <f>1+A47</f>
-        <v>12</v>
+        <f t="shared" si="1"/>
+        <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C48" s="3">
         <v>1</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E48" s="3">
-        <v>45.7502</v>
+        <v>43.0642</v>
       </c>
       <c r="F48" s="3">
-        <v>-108.57</v>
+        <v>-108.46</v>
       </c>
       <c r="G48" s="3">
-        <v>461.48398607652422</v>
+        <v>437.82235791428252</v>
       </c>
       <c r="H48" s="4" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">        &lt;option value="KBYZ"&gt;KBYZ: Billings NWS, MT&lt;/option&gt;</v>
+        <v xml:space="preserve">        &lt;option value="KRIW"&gt;KRIW: Riverton NWS, WY&lt;/option&gt;</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="3">
-        <f>1+A48</f>
-        <v>13</v>
+        <f t="shared" si="1"/>
+        <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C49" s="3">
         <v>1</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E49" s="3">
-        <v>39.861699999999999</v>
+        <v>45.7502</v>
       </c>
       <c r="F49" s="3">
-        <v>-104.673</v>
+        <v>-108.57</v>
       </c>
       <c r="G49" s="3">
-        <v>483.89787803782338</v>
+        <v>461.48398607652422</v>
       </c>
       <c r="H49" s="4" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">        &lt;option value="KDEN"&gt;KDEN: Denver Intl Airport, CO&lt;/option&gt;</v>
+        <v xml:space="preserve">        &lt;option value="KBYZ"&gt;KBYZ: Billings NWS, MT&lt;/option&gt;</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="3">
-        <f>1+A49</f>
-        <v>14</v>
+        <f t="shared" si="1"/>
+        <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C50" s="3">
         <v>1</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E50" s="3">
-        <v>39.991999999999997</v>
+        <v>39.861699999999999</v>
       </c>
       <c r="F50" s="3">
-        <v>-105.261</v>
+        <v>-104.673</v>
       </c>
       <c r="G50" s="3">
-        <v>484.62654498579639</v>
+        <v>483.89787803782338</v>
       </c>
       <c r="H50" s="4" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">        &lt;option value="KBOU"&gt;KBOU: Boulder NWS, CO&lt;/option&gt;</v>
+        <v xml:space="preserve">        &lt;option value="KDEN"&gt;KDEN: Denver Intl Airport, CO&lt;/option&gt;</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="3">
-        <f>1+A50</f>
-        <v>15</v>
+        <f t="shared" si="1"/>
+        <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C51" s="3">
         <v>1</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E51" s="3">
-        <v>43.582000000000001</v>
+        <v>39.991999999999997</v>
       </c>
       <c r="F51" s="3">
-        <v>-96.741900000000001</v>
+        <v>-105.261</v>
       </c>
       <c r="G51" s="3">
-        <v>521.33382524072977</v>
+        <v>484.62654498579639</v>
       </c>
       <c r="H51" s="4" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">        &lt;option value="KFSD"&gt;KFSD: Sioux Falls NWS, SD&lt;/option&gt;</v>
+        <v xml:space="preserve">        &lt;option value="KBOU"&gt;KBOU: Boulder NWS, CO&lt;/option&gt;</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="3">
-        <f>1+A51</f>
-        <v>16</v>
+        <f t="shared" si="1"/>
+        <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C52" s="3">
         <v>1</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E52" s="3">
-        <v>48.212400000000002</v>
+        <v>43.582000000000001</v>
       </c>
       <c r="F52" s="3">
-        <v>-106.61499999999999</v>
+        <v>-96.741900000000001</v>
       </c>
       <c r="G52" s="3">
-        <v>529.60258153152961</v>
+        <v>521.33382524072977</v>
       </c>
       <c r="H52" s="4" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">        &lt;option value="KGGW"&gt;KGGW: Glasgow NWS, MT&lt;/option&gt;</v>
+        <v xml:space="preserve">        &lt;option value="KFSD"&gt;KFSD: Sioux Falls NWS, SD&lt;/option&gt;</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="3">
-        <f>1+A52</f>
-        <v>17</v>
+        <f t="shared" si="1"/>
+        <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C53" s="3">
         <v>1</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E53" s="3">
-        <v>39.370699999999999</v>
+        <v>48.212400000000002</v>
       </c>
       <c r="F53" s="3">
-        <v>-101.699</v>
+        <v>-106.61499999999999</v>
       </c>
       <c r="G53" s="3">
-        <v>537.81299158903198</v>
+        <v>529.60258153152961</v>
       </c>
       <c r="H53" s="4" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">        &lt;option value="KGLD"&gt;KGLD: Goodland NWS, KS&lt;/option&gt;</v>
+        <v xml:space="preserve">        &lt;option value="KGGW"&gt;KGGW: Glasgow NWS, MT&lt;/option&gt;</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="3">
-        <f>1+A53</f>
-        <v>18</v>
+        <f t="shared" si="1"/>
+        <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C54" s="3">
         <v>1</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E54" s="3">
-        <v>40.647500000000001</v>
+        <v>39.370699999999999</v>
       </c>
       <c r="F54" s="3">
-        <v>-98.383700000000005</v>
+        <v>-101.699</v>
       </c>
       <c r="G54" s="3">
-        <v>549.60430011219228</v>
+        <v>537.81299158903198</v>
       </c>
       <c r="H54" s="4" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">        &lt;option value="KGID"&gt;KGID: Hastings NWS, NE&lt;/option&gt;</v>
+        <v xml:space="preserve">        &lt;option value="KGLD"&gt;KGLD: Goodland NWS, KS&lt;/option&gt;</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="3">
-        <f>1+A54</f>
-        <v>19</v>
+        <f t="shared" si="1"/>
+        <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C55" s="3">
         <v>1</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E55" s="3">
-        <v>48.667499999999997</v>
+        <v>40.647500000000001</v>
       </c>
       <c r="F55" s="3">
-        <v>-98.834400000000002</v>
+        <v>-98.383700000000005</v>
       </c>
       <c r="G55" s="3">
-        <v>610.75548649454925</v>
+        <v>549.60430011219228</v>
       </c>
       <c r="H55" s="4" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">        &lt;option value="MUNS"&gt;MUNS: Munich School, ND&lt;/option&gt;</v>
+        <v xml:space="preserve">        &lt;option value="KGID"&gt;KGID: Hastings NWS, NE&lt;/option&gt;</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="3">
-        <f>1+A55</f>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C56" s="3">
         <v>1</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E56" s="3">
-        <v>47.921900000000001</v>
+        <v>48.667499999999997</v>
       </c>
       <c r="F56" s="3">
-        <v>-97.098100000000002</v>
+        <v>-98.834400000000002</v>
       </c>
       <c r="G56" s="3">
-        <v>636.5233353769745</v>
+        <v>610.75548649454925</v>
       </c>
       <c r="H56" s="4" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">        &lt;option value="KFGF"&gt;KFGF: Grand Forks NWS, ND&lt;/option&gt;</v>
+        <v xml:space="preserve">        &lt;option value="MUNS"&gt;MUNS: Munich School, ND&lt;/option&gt;</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="3">
-        <f>1+A56</f>
-        <v>21</v>
+        <f t="shared" si="1"/>
+        <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C57" s="3">
         <v>1</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E57" s="3">
-        <v>41.319699999999997</v>
+        <v>47.921900000000001</v>
       </c>
       <c r="F57" s="3">
-        <v>-96.3673</v>
+        <v>-97.098100000000002</v>
       </c>
       <c r="G57" s="3">
-        <v>637.07875462019854</v>
+        <v>636.5233353769745</v>
       </c>
       <c r="H57" s="4" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">        &lt;option value="KOAX"&gt;KOAX: Omaha-Valley NWS, NE&lt;/option&gt;</v>
+        <v xml:space="preserve">        &lt;option value="KFGF"&gt;KFGF: Grand Forks NWS, ND&lt;/option&gt;</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="3">
-        <f>1+A57</f>
-        <v>22</v>
+        <f t="shared" si="1"/>
+        <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C58" s="3">
         <v>1</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E58" s="3">
-        <v>39.122399999999999</v>
+        <v>41.319699999999997</v>
       </c>
       <c r="F58" s="3">
-        <v>-108.527</v>
+        <v>-96.3673</v>
       </c>
       <c r="G58" s="3">
-        <v>706.05970680141979</v>
+        <v>637.07875462019854</v>
       </c>
       <c r="H58" s="4" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">        &lt;option value="KGJT"&gt;KGJT: Grand Junction NWS, CO&lt;/option&gt;</v>
+        <v xml:space="preserve">        &lt;option value="KOAX"&gt;KOAX: Omaha-Valley NWS, NE&lt;/option&gt;</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="3">
-        <f>1+A58</f>
-        <v>23</v>
+        <f t="shared" si="1"/>
+        <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C59" s="3">
         <v>1</v>
       </c>
       <c r="D59" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E59" s="3">
+        <v>39.122399999999999</v>
+      </c>
+      <c r="F59" s="3">
+        <v>-108.527</v>
+      </c>
+      <c r="G59" s="3">
+        <v>706.05970680141979</v>
+      </c>
+      <c r="H59" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        &lt;option value="KGJT"&gt;KGJT: Grand Junction NWS, CO&lt;/option&gt;</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="3">
+        <f t="shared" si="1"/>
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C60" s="3">
+        <v>1</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E60" s="3">
         <v>39.068800000000003</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F60" s="3">
         <v>-95.622399999999999</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G60" s="3">
         <v>840.71703075227481</v>
       </c>
-      <c r="H59" s="4" t="str">
+      <c r="H60" s="4" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">        &lt;option value="KTOP"&gt;KTOP: Topeka NWS, KS&lt;/option&gt;</v>
       </c>
@@ -2436,5 +2483,6 @@
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>